--- a/src/assets/accounts.xlsx
+++ b/src/assets/accounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE81E6F-DA8D-4946-AD7E-31872B86F0A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE58032-38C7-4590-8576-CDD4710EF5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5941" uniqueCount="1341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5949" uniqueCount="1343">
   <si>
     <t>Name</t>
   </si>
@@ -4048,6 +4048,12 @@
   </si>
   <si>
     <t>SHITU</t>
+  </si>
+  <si>
+    <t>malkeet rinku</t>
+  </si>
+  <si>
+    <t>0248</t>
   </si>
 </sst>
 </file>
@@ -29770,7 +29776,7 @@
     </row>
     <row r="2310" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2310" t="s">
-        <v>1306</v>
+        <v>1068</v>
       </c>
       <c r="B2310" s="6" t="s">
         <v>52</v>
@@ -31820,6 +31826,39 @@
       </c>
       <c r="C2497" s="4">
         <v>1417</v>
+      </c>
+    </row>
+    <row r="2498" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2498" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B2498" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2498" s="4" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="2499" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2499" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B2499" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2499" s="4" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="2500" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2500" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B2500" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2500" s="4">
+        <v>2258</v>
       </c>
     </row>
     <row r="1048572" spans="1:2" ht="12.75" x14ac:dyDescent="0.2"/>
